--- a/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,15; 40,54</t>
+          <t>29,46; 40,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,09; 51,88</t>
+          <t>39,91; 51,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,53; 44,74</t>
+          <t>32,16; 44,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,67</t>
+          <t>3,73; 8,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,79; 49,8</t>
+          <t>36,48; 49,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,14; 62,0</t>
+          <t>50,15; 62,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,51; 47,31</t>
+          <t>35,79; 48,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,41</t>
+          <t>6,12; 11,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,2; 43,1</t>
+          <t>34,44; 43,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,39; 55,29</t>
+          <t>46,38; 54,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,41; 44,12</t>
+          <t>35,73; 44,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,04</t>
+          <t>5,55; 9,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,4; 27,1</t>
+          <t>19,31; 27,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,89; 49,93</t>
+          <t>40,17; 49,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,9; 30,75</t>
+          <t>22,69; 30,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 14,12</t>
+          <t>8,0; 14,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,87; 35,12</t>
+          <t>26,84; 35,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,75; 54,79</t>
+          <t>45,67; 54,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,59; 38,47</t>
+          <t>30,33; 38,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,96</t>
+          <t>16,75; 22,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,23; 29,94</t>
+          <t>24,17; 30,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,73; 51,06</t>
+          <t>44,68; 51,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,49; 33,34</t>
+          <t>27,36; 33,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 17,54</t>
+          <t>13,07; 17,4</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,77; 39,16</t>
+          <t>28,7; 39,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,07; 50,7</t>
+          <t>39,1; 50,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 31,21</t>
+          <t>22,04; 31,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 16,09</t>
+          <t>9,07; 15,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,75; 41,61</t>
+          <t>30,94; 41,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,73; 56,72</t>
+          <t>45,35; 57,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,43; 35,88</t>
+          <t>25,47; 35,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,48</t>
+          <t>10,39; 16,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,8</t>
+          <t>31,5; 38,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,08; 52,01</t>
+          <t>44,07; 51,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 31,75</t>
+          <t>24,91; 31,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 15,21</t>
+          <t>10,78; 15,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,32; 33,75</t>
+          <t>23,97; 34,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,06; 55,52</t>
+          <t>44,1; 55,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,26; 34,81</t>
+          <t>25,38; 35,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 20,81</t>
+          <t>11,18; 21,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 43,1</t>
+          <t>33,68; 42,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,74; 60,76</t>
+          <t>50,58; 60,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,66; 44,61</t>
+          <t>34,82; 44,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 17,32</t>
+          <t>7,91; 17,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,09</t>
+          <t>30,35; 37,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,25; 56,86</t>
+          <t>49,03; 57,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,39; 38,35</t>
+          <t>31,34; 38,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 17,52</t>
+          <t>9,97; 17,31</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,38; 29,77</t>
+          <t>17,47; 29,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,53; 54,8</t>
+          <t>40,25; 54,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,71; 49,21</t>
+          <t>36,45; 49,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,71</t>
+          <t>7,45; 16,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,61; 37,14</t>
+          <t>24,3; 37,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,54; 63,44</t>
+          <t>49,56; 63,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,77; 53,74</t>
+          <t>40,34; 53,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,09</t>
+          <t>5,06; 13,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,65; 30,94</t>
+          <t>22,52; 31,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,2; 56,92</t>
+          <t>46,36; 56,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39,98; 49,52</t>
+          <t>40,2; 49,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 12,37</t>
+          <t>6,81; 12,64</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,54; 40,81</t>
+          <t>29,2; 40,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,31; 51,27</t>
+          <t>38,78; 51,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,16; 34,61</t>
+          <t>23,47; 34,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,91; 21,75</t>
+          <t>13,78; 21,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,38; 35,49</t>
+          <t>23,56; 34,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,45; 57,02</t>
+          <t>45,54; 57,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,5; 39,02</t>
+          <t>27,3; 39,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,96; 28,48</t>
+          <t>19,75; 28,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,6; 36,28</t>
+          <t>28,16; 36,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,79; 52,29</t>
+          <t>44,03; 52,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,71; 35,4</t>
+          <t>27,29; 35,54</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,64; 23,94</t>
+          <t>17,81; 23,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,1; 32,62</t>
+          <t>25,46; 32,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,16; 48,24</t>
+          <t>40,21; 48,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,13; 29,97</t>
+          <t>23,03; 30,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,95</t>
+          <t>3,62; 7,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,4; 43,37</t>
+          <t>35,39; 42,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,82; 52,5</t>
+          <t>44,33; 52,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,65; 40,06</t>
+          <t>32,86; 40,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 59,89</t>
+          <t>6,79; 64,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,3; 36,77</t>
+          <t>31,46; 36,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,6; 49,25</t>
+          <t>43,89; 49,24</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,12; 34,38</t>
+          <t>28,98; 34,11</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 50,5</t>
+          <t>5,84; 47,8</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,62; 32,36</t>
+          <t>25,55; 32,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,6; 45,24</t>
+          <t>37,86; 45,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,82; 39,68</t>
+          <t>32,27; 39,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 23,3</t>
+          <t>7,12; 23,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,51; 34,05</t>
+          <t>27,92; 34,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,78; 54,01</t>
+          <t>47,32; 54,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,69; 49,2</t>
+          <t>42,09; 48,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,05; 33,9</t>
+          <t>27,83; 33,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,76; 32,44</t>
+          <t>27,46; 32,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43,7; 48,67</t>
+          <t>43,67; 48,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38,43; 43,4</t>
+          <t>38,45; 43,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,04; 27,33</t>
+          <t>14,96; 27,42</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,44; 30,83</t>
+          <t>27,54; 30,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,15; 46,51</t>
+          <t>43,05; 46,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,7; 32,72</t>
+          <t>29,72; 32,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,38</t>
+          <t>9,34; 13,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,87; 36,05</t>
+          <t>32,93; 36,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,93; 53,43</t>
+          <t>49,94; 53,44</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,04; 40,48</t>
+          <t>37,14; 40,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,39; 36,32</t>
+          <t>16,32; 35,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,68; 32,91</t>
+          <t>30,84; 33,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46,82; 49,42</t>
+          <t>47,12; 49,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,91; 36,26</t>
+          <t>33,92; 36,24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,87; 26,0</t>
+          <t>13,97; 23,9</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79576; 110679</t>
+          <t>80441; 111242</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115199; 152897</t>
+          <t>117639; 150863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95573; 131423</t>
+          <t>94467; 130460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11264; 27009</t>
+          <t>11623; 27921</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95961; 129899</t>
+          <t>95149; 129181</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>144025; 178097</t>
+          <t>144050; 180936</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>102506; 136583</t>
+          <t>103328; 138804</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18408; 33052</t>
+          <t>17739; 32429</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>182557; 230082</t>
+          <t>183856; 229810</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>269959; 321756</t>
+          <t>269947; 317185</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206260; 257009</t>
+          <t>208111; 256803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33369; 54319</t>
+          <t>33345; 54983</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95679; 133645</t>
+          <t>95210; 136187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206692; 252418</t>
+          <t>203071; 251812</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115076; 154562</t>
+          <t>114031; 154202</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41358; 73201</t>
+          <t>41478; 73724</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>135393; 176968</t>
+          <t>135248; 176604</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>239624; 286962</t>
+          <t>239211; 285255</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154804; 201226</t>
+          <t>158638; 202394</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85227; 118212</t>
+          <t>86247; 116862</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241548; 298462</t>
+          <t>241004; 299249</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>460355; 525519</t>
+          <t>459885; 526140</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281967; 341918</t>
+          <t>280619; 340275</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>133958; 181262</t>
+          <t>135057; 179770</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91737; 124870</t>
+          <t>91497; 126345</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126611; 164295</t>
+          <t>126696; 163230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70068; 99427</t>
+          <t>70218; 101577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28192; 50852</t>
+          <t>28673; 49567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103131; 139576</t>
+          <t>103791; 138099</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>155938; 193429</t>
+          <t>154641; 195353</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85535; 120673</t>
+          <t>85668; 119854</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36865; 57545</t>
+          <t>36283; 58190</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>203789; 253871</t>
+          <t>206086; 253378</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>293162; 345911</t>
+          <t>293073; 344993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163203; 207930</t>
+          <t>163130; 207515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69159; 101166</t>
+          <t>71693; 101943</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>87212; 121044</t>
+          <t>85976; 123287</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>164778; 207626</t>
+          <t>164909; 206403</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93436; 128782</t>
+          <t>93898; 130319</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34884; 65038</t>
+          <t>34936; 67761</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>123975; 160080</t>
+          <t>125116; 158910</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>197348; 236317</t>
+          <t>196713; 236852</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134245; 172756</t>
+          <t>134841; 174004</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38242; 82394</t>
+          <t>37606; 83124</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>219757; 270772</t>
+          <t>221594; 272407</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>375733; 433769</t>
+          <t>374086; 435352</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237684; 290429</t>
+          <t>237340; 294161</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80730; 138130</t>
+          <t>78613; 136445</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37358; 60530</t>
+          <t>35519; 59363</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86184; 116506</t>
+          <t>85582; 115008</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>75426; 103934</t>
+          <t>76992; 105081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13666; 28082</t>
+          <t>13321; 29430</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51106; 77131</t>
+          <t>50466; 77771</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108781; 139309</t>
+          <t>108821; 138665</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89122; 117467</t>
+          <t>88171; 116932</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12069; 33867</t>
+          <t>13099; 34029</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>93072; 127166</t>
+          <t>92542; 130327</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204000; 245994</t>
+          <t>200353; 245585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>171828; 212857</t>
+          <t>172766; 213452</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29638; 54128</t>
+          <t>29802; 55320</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79992; 110520</t>
+          <t>79066; 110324</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>107709; 140478</t>
+          <t>106240; 140177</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63571; 91075</t>
+          <t>61764; 91484</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37496; 58646</t>
+          <t>37164; 58589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67804; 98713</t>
+          <t>65532; 96483</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>127279; 159666</t>
+          <t>127516; 160053</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>75106; 106576</t>
+          <t>74569; 107077</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>51318; 73212</t>
+          <t>50757; 73298</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>157012; 199143</t>
+          <t>154567; 198848</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>242599; 289716</t>
+          <t>243938; 290855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>148565; 189853</t>
+          <t>146318; 190570</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92927; 126094</t>
+          <t>93815; 125830</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154384; 200618</t>
+          <t>156569; 200626</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>266196; 319709</t>
+          <t>266519; 321406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>151841; 196755</t>
+          <t>151191; 197658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22923; 49619</t>
+          <t>22625; 48377</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>225960; 276784</t>
+          <t>225839; 273610</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>310965; 364289</t>
+          <t>307562; 363395</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>225722; 276932</t>
+          <t>227142; 278123</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>56886; 508663</t>
+          <t>57696; 548124</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>392208; 460837</t>
+          <t>394243; 460570</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>591434; 668134</t>
+          <t>595457; 668053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>392514; 463370</t>
+          <t>390557; 459785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86112; 744103</t>
+          <t>86074; 704376</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>190586; 240721</t>
+          <t>190068; 240336</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>292917; 352488</t>
+          <t>294932; 355138</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>255533; 308968</t>
+          <t>251279; 306687</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71405; 216387</t>
+          <t>66117; 215118</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>215546; 266761</t>
+          <t>218718; 267843</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>385408; 445002</t>
+          <t>389886; 444985</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>344447; 406457</t>
+          <t>347754; 404591</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>201294; 243346</t>
+          <t>199770; 242880</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>424005; 495495</t>
+          <t>419324; 493673</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>700446; 780080</t>
+          <t>700057; 779444</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>616687; 696456</t>
+          <t>616966; 693369</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>231179; 449981</t>
+          <t>246266; 451538</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>899229; 1010203</t>
+          <t>902370; 1007998</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1478659; 1593946</t>
+          <t>1475400; 1592229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1007995; 1110714</t>
+          <t>1008815; 1117687</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>332435; 462865</t>
+          <t>323099; 461845</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1110807; 1218215</t>
+          <t>1112673; 1224850</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1776561; 1901319</t>
+          <t>1777181; 1901415</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1312864; 1434726</t>
+          <t>1316269; 1436404</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>608615; 1348448</t>
+          <t>605896; 1323806</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2042280; 2190236</t>
+          <t>2052399; 2205057</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3270192; 3452205</t>
+          <t>3291292; 3461983</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2353086; 2516177</t>
+          <t>2353450; 2514349</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>995109; 1864797</t>
+          <t>1002271; 1713776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,46; 40,75</t>
+          <t>28,95; 40,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,91; 51,19</t>
+          <t>39,29; 51,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,16; 44,41</t>
+          <t>31,6; 44,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,96</t>
+          <t>3,69; 8,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,48; 49,53</t>
+          <t>36,35; 49,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,15; 62,99</t>
+          <t>49,79; 62,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,79; 48,08</t>
+          <t>36,0; 47,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,2</t>
+          <t>6,5; 11,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,44; 43,05</t>
+          <t>34,88; 43,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,38; 54,5</t>
+          <t>46,36; 54,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35,73; 44,09</t>
+          <t>35,92; 44,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,15</t>
+          <t>5,89; 9,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,31; 27,62</t>
+          <t>19,26; 26,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,17; 49,81</t>
+          <t>40,44; 49,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,69; 30,68</t>
+          <t>22,71; 30,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,0; 14,22</t>
+          <t>8,61; 15,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,84; 35,04</t>
+          <t>26,92; 35,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,67; 54,46</t>
+          <t>45,99; 55,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,33; 38,69</t>
+          <t>30,37; 38,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,75; 22,69</t>
+          <t>17,6; 23,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,17; 30,01</t>
+          <t>24,28; 29,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,68; 51,12</t>
+          <t>44,55; 50,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,36; 33,18</t>
+          <t>27,59; 33,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,07; 17,4</t>
+          <t>14,24; 18,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 39,63</t>
+          <t>28,6; 38,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 50,37</t>
+          <t>38,58; 49,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,04; 31,89</t>
+          <t>21,51; 31,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,07; 15,68</t>
+          <t>9,25; 16,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,94; 41,17</t>
+          <t>30,71; 41,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,35; 57,28</t>
+          <t>45,07; 56,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 35,64</t>
+          <t>25,45; 35,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 16,67</t>
+          <t>10,28; 16,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,5; 38,73</t>
+          <t>31,06; 38,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,07; 51,87</t>
+          <t>44,06; 51,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,91; 31,69</t>
+          <t>25,18; 31,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,78; 15,33</t>
+          <t>10,32; 14,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 34,37</t>
+          <t>23,84; 33,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,1; 55,19</t>
+          <t>44,22; 55,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,22</t>
+          <t>25,62; 35,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 21,68</t>
+          <t>11,52; 21,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,68; 42,78</t>
+          <t>33,33; 43,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 60,9</t>
+          <t>50,88; 60,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,82; 44,93</t>
+          <t>34,85; 45,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,91; 17,47</t>
+          <t>13,95; 20,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,35; 37,31</t>
+          <t>30,61; 37,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 57,06</t>
+          <t>49,12; 56,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 38,85</t>
+          <t>31,4; 38,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 17,31</t>
+          <t>14,03; 19,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 29,2</t>
+          <t>18,03; 30,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,25; 54,09</t>
+          <t>40,89; 55,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,45; 49,75</t>
+          <t>35,42; 49,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,47</t>
+          <t>7,63; 15,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 37,45</t>
+          <t>24,52; 37,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,56; 63,15</t>
+          <t>49,44; 63,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,34; 53,49</t>
+          <t>40,58; 53,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,15</t>
+          <t>9,29; 15,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 31,71</t>
+          <t>22,65; 31,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,36; 56,82</t>
+          <t>47,23; 57,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,2; 49,66</t>
+          <t>40,22; 49,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 12,64</t>
+          <t>9,33; 14,56</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,2; 40,74</t>
+          <t>29,63; 40,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38,78; 51,16</t>
+          <t>39,02; 51,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,47; 34,77</t>
+          <t>24,09; 34,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,78; 21,73</t>
+          <t>14,49; 22,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23,56; 34,69</t>
+          <t>24,4; 35,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,54; 57,16</t>
+          <t>45,29; 57,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,3; 39,21</t>
+          <t>27,9; 39,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,75; 28,51</t>
+          <t>19,88; 27,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,16; 36,22</t>
+          <t>28,16; 36,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,03; 52,5</t>
+          <t>43,82; 52,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,29; 35,54</t>
+          <t>27,56; 35,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,81; 23,89</t>
+          <t>18,08; 24,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,46; 32,62</t>
+          <t>25,28; 32,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,21; 48,49</t>
+          <t>40,53; 48,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,03; 30,11</t>
+          <t>23,06; 30,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,75</t>
+          <t>3,91; 7,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,39; 42,87</t>
+          <t>35,17; 43,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,33; 52,37</t>
+          <t>44,39; 52,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,86; 40,23</t>
+          <t>32,83; 40,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,79; 64,54</t>
+          <t>6,61; 10,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,46; 36,75</t>
+          <t>31,61; 36,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43,89; 49,24</t>
+          <t>43,59; 49,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28,98; 34,11</t>
+          <t>29,21; 34,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 47,8</t>
+          <t>5,8; 8,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>25,55; 32,31</t>
+          <t>25,39; 32,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,86; 45,58</t>
+          <t>38,14; 45,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,27; 39,39</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 23,16</t>
+          <t>20,01; 26,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,92; 34,19</t>
+          <t>27,74; 34,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,32; 54,01</t>
+          <t>46,86; 54,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,09; 48,97</t>
+          <t>41,78; 48,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,83; 33,84</t>
+          <t>28,79; 34,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,46; 32,32</t>
+          <t>27,35; 32,16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43,67; 48,63</t>
+          <t>43,72; 48,66</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38,45; 43,21</t>
+          <t>38,46; 43,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,96; 27,42</t>
+          <t>25,39; 29,62</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,76</t>
+          <t>27,69; 30,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,05; 46,46</t>
+          <t>43,01; 46,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29,72; 32,93</t>
+          <t>29,68; 32,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,35</t>
+          <t>12,4; 14,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,93; 36,25</t>
+          <t>32,84; 36,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,94; 53,44</t>
+          <t>49,9; 53,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,14; 40,52</t>
+          <t>37,04; 40,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16,32; 35,66</t>
+          <t>16,95; 19,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,84; 33,13</t>
+          <t>30,74; 33,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47,12; 49,56</t>
+          <t>47,08; 49,53</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,24</t>
+          <t>33,89; 36,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,97; 23,9</t>
+          <t>15,09; 16,8</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24737</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>47216</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80441; 111242</t>
+          <t>79037; 110360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>117639; 150863</t>
+          <t>115801; 150754</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94467; 130460</t>
+          <t>92840; 129509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11623; 27921</t>
+          <t>11762; 27694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95149; 129181</t>
+          <t>94813; 128352</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>144050; 180936</t>
+          <t>143006; 178551</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>103328; 138804</t>
+          <t>103936; 136924</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17739; 32429</t>
+          <t>20538; 36235</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>183856; 229810</t>
+          <t>186195; 231074</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>269947; 317185</t>
+          <t>269835; 318499</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208111; 256803</t>
+          <t>209241; 258095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33345; 54983</t>
+          <t>37388; 58817</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>101314</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>157163</t>
+          <t>175299</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95210; 136187</t>
+          <t>94949; 132762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>203071; 251812</t>
+          <t>204416; 249405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114031; 154202</t>
+          <t>114134; 154937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41478; 73724</t>
+          <t>45689; 82690</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>135248; 176604</t>
+          <t>135673; 176851</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>239211; 285255</t>
+          <t>240875; 288897</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>158638; 202394</t>
+          <t>158872; 200305</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86247; 116862</t>
+          <t>96179; 130928</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>241004; 299249</t>
+          <t>242085; 299008</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>459885; 526140</t>
+          <t>458582; 521930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280619; 340275</t>
+          <t>283019; 343830</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135057; 179770</t>
+          <t>153425; 199206</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>39084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>45707</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84256</t>
+          <t>84792</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>91497; 126345</t>
+          <t>91186; 123833</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126696; 163230</t>
+          <t>125030; 161250</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70218; 101577</t>
+          <t>68520; 98800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28673; 49567</t>
+          <t>29242; 51953</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103791; 138099</t>
+          <t>103000; 137608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>154641; 195353</t>
+          <t>153684; 194151</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85668; 119854</t>
+          <t>85581; 118196</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36283; 58190</t>
+          <t>36637; 58173</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>206086; 253378</t>
+          <t>203234; 253860</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>293073; 344993</t>
+          <t>293007; 344677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163130; 207515</t>
+          <t>164877; 208997</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71693; 101943</t>
+          <t>69403; 98988</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48647</t>
+          <t>61134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>71947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>111429</t>
+          <t>133081</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85976; 123287</t>
+          <t>85490; 121787</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>164909; 206403</t>
+          <t>165359; 207133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93898; 130319</t>
+          <t>94783; 130072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34936; 67761</t>
+          <t>42983; 81296</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>125116; 158910</t>
+          <t>123789; 160860</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>196713; 236852</t>
+          <t>197896; 236132</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134841; 174004</t>
+          <t>134959; 175366</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>37606; 83124</t>
+          <t>58884; 87411</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>221594; 272407</t>
+          <t>223469; 273671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>374086; 435352</t>
+          <t>374787; 431354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237340; 294161</t>
+          <t>237757; 293514</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>78613; 136445</t>
+          <t>111521; 157364</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43639</t>
+          <t>50562</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35519; 59363</t>
+          <t>36664; 61136</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85582; 115008</t>
+          <t>86930; 117512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76992; 105081</t>
+          <t>74813; 103987</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13321; 29430</t>
+          <t>15701; 32884</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50466; 77771</t>
+          <t>50923; 77133</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108821; 138665</t>
+          <t>108561; 139398</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88171; 116932</t>
+          <t>88700; 117426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13099; 34029</t>
+          <t>21270; 34693</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92542; 130327</t>
+          <t>93083; 129509</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200353; 245585</t>
+          <t>204147; 247108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>172766; 213452</t>
+          <t>172871; 213347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29802; 55320</t>
+          <t>40535; 63260</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>62549</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>108557</t>
+          <t>112048</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>79066; 110324</t>
+          <t>80234; 110893</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>106240; 140177</t>
+          <t>106914; 140144</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61764; 91484</t>
+          <t>63381; 91747</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37164; 58589</t>
+          <t>39234; 62206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>65532; 96483</t>
+          <t>67862; 97557</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>127516; 160053</t>
+          <t>126824; 161462</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74569; 107077</t>
+          <t>76195; 106991</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50757; 73298</t>
+          <t>52430; 73627</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>154567; 198848</t>
+          <t>154588; 199392</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>243938; 290855</t>
+          <t>242743; 290781</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>146318; 190570</t>
+          <t>147809; 192456</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93815; 125830</t>
+          <t>96620; 128259</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>41201</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>251460</t>
+          <t>63507</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>284668</t>
+          <t>104709</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>156569; 200626</t>
+          <t>155479; 200527</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>266519; 321406</t>
+          <t>268640; 323316</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>151191; 197658</t>
+          <t>151410; 199793</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22625; 48377</t>
+          <t>28123; 56017</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>225839; 273610</t>
+          <t>224434; 275210</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>307562; 363395</t>
+          <t>308029; 362478</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>227142; 278123</t>
+          <t>226972; 281603</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57696; 548124</t>
+          <t>51028; 78875</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>394243; 460570</t>
+          <t>396177; 461362</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>595457; 668053</t>
+          <t>591378; 667831</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>390557; 459785</t>
+          <t>393676; 460703</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>86074; 704376</t>
+          <t>86512; 126315</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152045</t>
+          <t>183620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>221525</t>
+          <t>261303</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>373570</t>
+          <t>444923</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>190068; 240336</t>
+          <t>188872; 239046</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>294932; 355138</t>
+          <t>297175; 354009</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>251279; 306687</t>
+          <t>253415; 304978</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66117; 215118</t>
+          <t>159726; 209898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>218718; 267843</t>
+          <t>217372; 269239</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>389886; 444985</t>
+          <t>386087; 446998</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>347754; 404591</t>
+          <t>345135; 403728</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>199770; 242880</t>
+          <t>239330; 286915</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>419324; 493673</t>
+          <t>417737; 491170</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>700057; 779444</t>
+          <t>700793; 779978</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>616966; 693369</t>
+          <t>617119; 693488</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>246266; 451538</t>
+          <t>413682; 482710</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>902370; 1007998</t>
+          <t>907289; 1008885</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1475400; 1592229</t>
+          <t>1473734; 1595276</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1008815; 1117687</t>
+          <t>1007320; 1112032</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>323099; 461845</t>
+          <t>438065; 523629</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1112673; 1224850</t>
+          <t>1109829; 1221313</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1777181; 1901415</t>
+          <t>1775443; 1895160</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1316269; 1436404</t>
+          <t>1312919; 1430779</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>605896; 1323806</t>
+          <t>633462; 716404</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2052399; 2205057</t>
+          <t>2046214; 2200666</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3291292; 3461983</t>
+          <t>3288658; 3459538</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2353450; 2514349</t>
+          <t>2351851; 2520436</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1002271; 1713776</t>
+          <t>1096644; 1221522</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
